--- a/docs/項目定義.xlsx
+++ b/docs/項目定義.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
